--- a/data/trans_camb/P3A_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,68</t>
+          <t>-2,55; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,72</t>
+          <t>-3,26; 0,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 4,17</t>
+          <t>-2,34; 4,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,18</t>
+          <t>-1,34; 2,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,92</t>
+          <t>-2,03; 0,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,66</t>
+          <t>-1,28; 3,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,29</t>
+          <t>-1,39; 1,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,31</t>
+          <t>-1,93; 0,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,72</t>
+          <t>-1,55; 2,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 102,91</t>
+          <t>-65,34; 88,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 49,28</t>
+          <t>-80,63; 50,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,21; 208,05</t>
+          <t>-75,78; 184,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 279,0</t>
+          <t>-69,18; 287,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 136,51</t>
+          <t>-87,93; 128,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,77; 280,69</t>
+          <t>-72,64; 453,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,18; 83,31</t>
+          <t>-49,36; 77,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 27,99</t>
+          <t>-70,4; 24,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 140,24</t>
+          <t>-60,17; 153,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,3</t>
+          <t>-3,04; 0,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -1,59</t>
+          <t>-4,32; -1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,42</t>
+          <t>-3,86; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,52</t>
+          <t>-1,57; 1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,85</t>
+          <t>-1,88; 1,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,32</t>
+          <t>-2,38; 0,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,32</t>
+          <t>-1,88; 0,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,73</t>
+          <t>-2,76; -0,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,49</t>
+          <t>-2,8; -0,38</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 19,05</t>
+          <t>-71,52; 13,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -45,38</t>
+          <t>-100,0; -52,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,61</t>
+          <t>-100,0; 67,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 150,73</t>
+          <t>-64,47; 157,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,92; 83,18</t>
+          <t>-75,19; 108,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,92; 89,46</t>
+          <t>-92,31; 76,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,19; 19,53</t>
+          <t>-58,85; 20,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,55; -33,31</t>
+          <t>-84,61; -30,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,6; -7,78</t>
+          <t>-93,05; -3,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,71</t>
+          <t>-5,28; -0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -2,51</t>
+          <t>-6,52; -2,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -1,42</t>
+          <t>-5,84; -1,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,73</t>
+          <t>-1,54; 1,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,11</t>
+          <t>-2,99; 0,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,11</t>
+          <t>-3,0; -0,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,17</t>
+          <t>-2,59; -0,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; -1,57</t>
+          <t>-4,05; -1,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -1,08</t>
+          <t>-3,83; -1,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,73; -13,19</t>
+          <t>-77,17; -10,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,01; -58,36</t>
+          <t>-92,43; -58,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,81; -30,86</t>
+          <t>-84,41; -27,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 107,02</t>
+          <t>-50,38; 120,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,93; 15,93</t>
+          <t>-85,47; 25,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,17; -1,16</t>
+          <t>-81,79; 2,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 7,91</t>
+          <t>-59,22; 0,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,72; -50,26</t>
+          <t>-86,22; -49,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,65; -33,09</t>
+          <t>-79,92; -35,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,07</t>
+          <t>-3,69; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; -1,24</t>
+          <t>-5,24; -1,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,1</t>
+          <t>-4,37; 0,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,02</t>
+          <t>-1,09; 2,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,61</t>
+          <t>-2,24; 0,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,4</t>
+          <t>-0,96; 2,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,38</t>
+          <t>-1,78; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,57</t>
+          <t>-3,04; -0,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,93</t>
+          <t>-2,13; 0,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 43,01</t>
+          <t>-67,87; 43,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,04; -35,1</t>
+          <t>-90,76; -27,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 6,42</t>
+          <t>-81,56; 5,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 307,78</t>
+          <t>-44,25; 292,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,78; 59,07</t>
+          <t>-78,95; 76,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 241,43</t>
+          <t>-34,17; 233,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 68,81</t>
+          <t>-47,42; 57,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,23; -17,01</t>
+          <t>-80,56; -20,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 42,8</t>
+          <t>-55,18; 38,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,94</t>
+          <t>-3,25; 2,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,39</t>
+          <t>-2,32; 3,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,17</t>
+          <t>-3,14; 2,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,84</t>
+          <t>-0,06; 4,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,05</t>
+          <t>-2,46; 1,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,22</t>
+          <t>-1,14; 2,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,65</t>
+          <t>-1,0; 2,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,62</t>
+          <t>-1,79; 1,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,72</t>
+          <t>-1,23; 1,74</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 98,13</t>
+          <t>-65,95; 100,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 163,11</t>
+          <t>-50,89; 164,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 102,87</t>
+          <t>-57,09; 109,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 412,26</t>
+          <t>-7,81; 470,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 106,91</t>
+          <t>-83,0; 145,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 231,25</t>
+          <t>-38,94; 238,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 148,41</t>
+          <t>-31,78; 136,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 87,21</t>
+          <t>-50,45; 76,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 94,71</t>
+          <t>-33,81; 92,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 6,63</t>
+          <t>-0,14; 7,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,76</t>
+          <t>-3,73; 1,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,57</t>
+          <t>0,75; 6,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,44</t>
+          <t>-4,0; 2,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,69</t>
+          <t>-4,46; 1,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,94</t>
+          <t>-5,19; 2,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,22</t>
+          <t>-1,42; 3,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,39</t>
+          <t>-3,73; 0,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,39</t>
+          <t>-2,79; 3,5</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 396,9</t>
+          <t>-11,78; 398,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-87,97; 69,63</t>
+          <t>-85,31; 102,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,13; 450,41</t>
+          <t>14,5; 423,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-57,07; 68,97</t>
+          <t>-56,25; 56,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 49,55</t>
+          <t>-62,2; 51,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 64,3</t>
+          <t>-70,78; 61,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 96,72</t>
+          <t>-28,74; 97,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 13,75</t>
+          <t>-66,82; 15,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 92,84</t>
+          <t>-41,02; 96,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 14,24</t>
+          <t>1,91; 14,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 10,26</t>
+          <t>-0,07; 10,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,76; 18,24</t>
+          <t>6,89; 17,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,87; 13,82</t>
+          <t>3,7; 14,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,16</t>
+          <t>-1,1; 10,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,98; 22,29</t>
+          <t>12,6; 22,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,66</t>
+          <t>4,93; 12,93</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,21</t>
+          <t>0,81; 8,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,12; 18,88</t>
+          <t>12,3; 19,34</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,05; 211,33</t>
+          <t>14,29; 231,36</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 165,08</t>
+          <t>-4,92; 156,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>59,29; 286,01</t>
+          <t>55,81; 293,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,18; 176,28</t>
+          <t>26,44; 174,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 124,29</t>
+          <t>-10,07; 122,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>93,29; 290,54</t>
+          <t>89,45; 312,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,85; 156,22</t>
+          <t>39,66; 152,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,39; 104,48</t>
+          <t>6,82; 109,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>97,98; 242,67</t>
+          <t>102,78; 253,32</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,72</t>
+          <t>-1,24; 0,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,68</t>
+          <t>-2,55; -0,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,44</t>
+          <t>-0,82; 1,33</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,39</t>
+          <t>0,42; 2,3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,73</t>
+          <t>-0,97; 0,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,13</t>
+          <t>1,1; 3,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,33</t>
+          <t>-0,07; 1,24</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,2</t>
+          <t>-1,49; -0,21</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,98</t>
+          <t>0,38; 1,95</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 20,27</t>
+          <t>-26,95; 22,32</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-54,24; -19,28</t>
+          <t>-55,87; -21,45</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 39,43</t>
+          <t>-18,74; 36,84</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13,32; 86,73</t>
+          <t>11,17; 84,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 27,08</t>
+          <t>-28,0; 27,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,33; 115,71</t>
+          <t>32,24; 116,92</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 41,31</t>
+          <t>-2,03; 37,37</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-37,78; -6,05</t>
+          <t>-38,48; -7,08</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10,23; 60,35</t>
+          <t>10,12; 58,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,59</t>
+          <t>-2,55; 1,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,61</t>
+          <t>-3,04; 0,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,29</t>
+          <t>-2,37; 4,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,05</t>
+          <t>-1,29; 2,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,92</t>
+          <t>-1,9; 0,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,13</t>
+          <t>-1,64; 2,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,24</t>
+          <t>-1,36; 1,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,41</t>
+          <t>-1,98; 0,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,52</t>
+          <t>-1,43; 2,46</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 88,88</t>
+          <t>-66,05; 88,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,63; 50,36</t>
+          <t>-77,81; 58,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 184,48</t>
+          <t>-73,92; 231,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 287,31</t>
+          <t>-67,61; 307,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,93; 128,99</t>
+          <t>-88,03; 158,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,64; 453,13</t>
+          <t>-81,02; 287,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 77,84</t>
+          <t>-48,02; 72,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 24,93</t>
+          <t>-70,11; 33,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 153,61</t>
+          <t>-56,9; 150,15</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,17</t>
+          <t>-3,13; 0,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -1,52</t>
+          <t>-4,27; -1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,26</t>
+          <t>-4,01; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,41</t>
+          <t>-1,5; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,08</t>
+          <t>-1,81; 0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,4</t>
+          <t>-2,2; 0,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,37</t>
+          <t>-1,89; 0,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,74</t>
+          <t>-2,66; -0,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,38</t>
+          <t>-2,77; -0,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-75,6%</t>
+          <t>-74,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-58,88%</t>
+          <t>-54,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-70,41%</t>
+          <t>-68,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 13,11</t>
+          <t>-73,73; 26,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -52,58</t>
+          <t>-100,0; -46,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,0</t>
+          <t>-100,0; 69,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,47; 157,97</t>
+          <t>-60,32; 148,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 108,87</t>
+          <t>-78,11; 91,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,31; 76,33</t>
+          <t>-92,12; 76,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,85; 20,4</t>
+          <t>-61,59; 12,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,61; -30,67</t>
+          <t>-85,09; -31,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-93,05; -3,45</t>
+          <t>-92,45; 10,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,76</t>
+          <t>-5,42; -0,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -2,52</t>
+          <t>-6,39; -2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; -1,33</t>
+          <t>-5,73; -1,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,82</t>
+          <t>-1,8; 1,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,19</t>
+          <t>-2,7; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,08</t>
+          <t>-2,73; 0,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,02</t>
+          <t>-2,69; 0,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -1,62</t>
+          <t>-3,95; -1,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -1,26</t>
+          <t>-3,6; -1,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-66,4%</t>
+          <t>-66,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-56,15%</t>
+          <t>-49,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-63,14%</t>
+          <t>-60,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,17; -10,32</t>
+          <t>-78,31; -12,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,43; -58,71</t>
+          <t>-92,99; -59,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,41; -27,81</t>
+          <t>-84,19; -34,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 120,78</t>
+          <t>-56,97; 104,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 25,77</t>
+          <t>-87,29; 18,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,79; 2,78</t>
+          <t>-78,87; 14,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 0,27</t>
+          <t>-58,68; 7,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,22; -49,53</t>
+          <t>-86,07; -49,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,92; -35,74</t>
+          <t>-77,43; -32,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,03</t>
+          <t>-3,66; 0,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -1,1</t>
+          <t>-5,03; -1,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,25</t>
+          <t>-3,51; 1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,96</t>
+          <t>-1,08; 2,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,72</t>
+          <t>-2,38; 0,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,36</t>
+          <t>-0,78; 2,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,26</t>
+          <t>-1,66; 1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,55</t>
+          <t>-3,2; -0,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,88</t>
+          <t>-1,45; 1,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-46,43%</t>
+          <t>-24,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,97%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 43,19</t>
+          <t>-68,22; 38,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-90,76; -27,32</t>
+          <t>-90,05; -30,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,56; 5,74</t>
+          <t>-61,9; 45,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 292,46</t>
+          <t>-48,09; 298,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 76,68</t>
+          <t>-82,32; 67,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 233,82</t>
+          <t>-29,41; 206,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 57,65</t>
+          <t>-45,51; 60,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-80,56; -20,38</t>
+          <t>-80,2; -24,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 38,23</t>
+          <t>-38,79; 60,91</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1498,37 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,06</t>
+          <t>-3,32; 2,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,43</t>
+          <t>-2,5; 3,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,22</t>
+          <t>-2,91; 2,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,71</t>
+          <t>-0,06; 4,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,05</t>
+          <t>-2,38; 1,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,26</t>
+          <t>-1,35; 2,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,67</t>
+          <t>-1,02; 2,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,53</t>
+          <t>-1,8; 1,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,74</t>
+          <t>-1,39; 1,63</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,84%</t>
+          <t>-7,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 100,88</t>
+          <t>-62,92; 113,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 164,07</t>
+          <t>-52,03; 172,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 109,58</t>
+          <t>-54,26; 106,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 470,86</t>
+          <t>-11,35; 391,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 145,93</t>
+          <t>-77,21; 128,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 238,06</t>
+          <t>-44,45; 205,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 136,28</t>
+          <t>-28,99; 155,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,45; 76,4</t>
+          <t>-49,71; 86,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 92,29</t>
+          <t>-37,33; 86,3</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,16</t>
+          <t>-0,12; 6,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,11</t>
+          <t>-3,9; 0,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,47</t>
+          <t>0,95; 6,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,33</t>
+          <t>-4,15; 2,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,61</t>
+          <t>-4,78; 1,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,83</t>
+          <t>-1,28; 4,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,2</t>
+          <t>-1,51; 3,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,37</t>
+          <t>-3,4; 0,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,5</t>
+          <t>0,58; 4,97</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129,34%</t>
+          <t>127,41%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-13,01%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 398,57</t>
+          <t>-12,43; 380,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,31; 102,52</t>
+          <t>-86,76; 61,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14,5; 423,64</t>
+          <t>8,15; 386,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 56,73</t>
+          <t>-57,79; 78,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 51,53</t>
+          <t>-64,69; 40,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 61,36</t>
+          <t>-16,59; 141,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 97,98</t>
+          <t>-28,08; 101,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 15,48</t>
+          <t>-62,37; 20,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 96,01</t>
+          <t>8,67; 154,3</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,99</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,51</t>
+          <t>17,69</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15,69</t>
+          <t>15,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,91; 14,22</t>
+          <t>2,11; 14,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 10,45</t>
+          <t>-0,44; 9,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,89; 17,96</t>
+          <t>7,73; 17,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,7; 14,23</t>
+          <t>3,48; 14,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 10,12</t>
+          <t>-0,68; 9,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,6; 22,18</t>
+          <t>13,05; 22,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,93</t>
+          <t>4,61; 12,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,33</t>
+          <t>-0,06; 7,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,3; 19,34</t>
+          <t>12,06; 19,31</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142,99%</t>
+          <t>138,7%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>167,76%</t>
+          <t>169,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>158,22%</t>
+          <t>157,66%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,29; 231,36</t>
+          <t>15,39; 226,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 156,2</t>
+          <t>-5,52; 153,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55,81; 293,74</t>
+          <t>61,17; 292,4</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26,44; 174,37</t>
+          <t>24,69; 176,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 122,62</t>
+          <t>-5,64; 128,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>89,45; 312,21</t>
+          <t>91,42; 288,13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,66; 152,16</t>
+          <t>38,9; 156,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>6,82; 109,63</t>
+          <t>-0,2; 100,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>102,78; 253,32</t>
+          <t>98,35; 252,06</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,79</t>
+          <t>-1,18; 0,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,8</t>
+          <t>-2,43; -0,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,33</t>
+          <t>-0,61; 1,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,3</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,76</t>
+          <t>-0,91; 0,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,18</t>
+          <t>1,76; 3,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,24</t>
+          <t>-0,07; 1,32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,21</t>
+          <t>-1,42; -0,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,95</t>
+          <t>0,96; 2,25</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,32</t>
+          <t>-26,62; 22,06</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -21,45</t>
+          <t>-53,62; -20,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 36,84</t>
+          <t>-13,09; 41,45</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11,17; 84,88</t>
+          <t>13,0; 85,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 27,5</t>
+          <t>-25,83; 32,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,24; 116,92</t>
+          <t>46,96; 129,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 37,37</t>
+          <t>-1,86; 38,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-38,48; -7,08</t>
+          <t>-36,96; -6,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10,12; 58,92</t>
+          <t>23,91; 68,6</t>
         </is>
       </c>
     </row>
